--- a/data/trans_orig/P58-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P58-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2007</t>
+          <t>Población según su lugar de nacimiento en 2007 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46686</t>
+          <t>47220</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86076</t>
+          <t>85780</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23541</t>
+          <t>22708</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52202</t>
+          <t>51126</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75042</t>
+          <t>77301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122828</t>
+          <t>125407</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24963</t>
+          <t>25584</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57303</t>
+          <t>56344</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51406</t>
+          <t>51278</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86503</t>
+          <t>85033</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84543</t>
+          <t>84012</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>129852</t>
+          <t>131546</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>902162</t>
+          <t>903144</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>952078</t>
+          <t>950127</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1190664</t>
+          <t>1192680</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1235578</t>
+          <t>1233175</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2110364</t>
+          <t>2104294</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2174029</t>
+          <t>2170359</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78995</t>
+          <t>76247</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>126712</t>
+          <t>126652</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>115940</t>
+          <t>116948</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>175653</t>
+          <t>173456</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>203759</t>
+          <t>207425</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>278022</t>
+          <t>279450</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>127628</t>
+          <t>126841</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>187281</t>
+          <t>186964</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>106840</t>
+          <t>108086</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>152063</t>
+          <t>153000</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>245456</t>
+          <t>244432</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>320488</t>
+          <t>321081</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1402400</t>
+          <t>1400478</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1474751</t>
+          <t>1471738</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1279638</t>
+          <t>1283751</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1346813</t>
+          <t>1350305</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2711597</t>
+          <t>2707388</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2809527</t>
+          <t>2802511</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,41%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28490</t>
+          <t>27275</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59950</t>
+          <t>58557</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31634</t>
+          <t>33633</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63733</t>
+          <t>66270</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>68268</t>
+          <t>69900</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112919</t>
+          <t>115085</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60415</t>
+          <t>61369</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101820</t>
+          <t>102879</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41760</t>
+          <t>40937</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72198</t>
+          <t>72355</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110176</t>
+          <t>111570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162536</t>
+          <t>164692</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>406334</t>
+          <t>404726</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>453610</t>
+          <t>452769</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>353409</t>
+          <t>352360</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>392718</t>
+          <t>391780</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>773529</t>
+          <t>767771</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>837129</t>
+          <t>831774</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>175089</t>
+          <t>174306</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>239375</t>
+          <t>239426</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>188925</t>
+          <t>192710</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>260829</t>
+          <t>260917</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>385425</t>
+          <t>381417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>482913</t>
+          <t>484671</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>233863</t>
+          <t>235995</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>314410</t>
+          <t>316319</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>219556</t>
+          <t>220515</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>280947</t>
+          <t>282692</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>470374</t>
+          <t>476262</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>575599</t>
+          <t>580058</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2746504</t>
+          <t>2749724</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2845669</t>
+          <t>2847351</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2853356</t>
+          <t>2858073</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2950493</t>
+          <t>2946200</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5635560</t>
+          <t>5630879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5771939</t>
+          <t>5772031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2012</t>
+          <t>Población según su lugar de nacimiento en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38152</t>
+          <t>37916</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71544</t>
+          <t>69269</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37108</t>
+          <t>37218</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67716</t>
+          <t>66848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81230</t>
+          <t>80187</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>127068</t>
+          <t>125108</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51579</t>
+          <t>51132</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95775</t>
+          <t>95594</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55020</t>
+          <t>54841</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99594</t>
+          <t>99456</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>116805</t>
+          <t>117349</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>181367</t>
+          <t>182489</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>822157</t>
+          <t>823552</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>876377</t>
+          <t>876362</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1185710</t>
+          <t>1186077</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1235508</t>
+          <t>1237000</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2020957</t>
+          <t>2023992</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2097771</t>
+          <t>2099391</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,79%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99010</t>
+          <t>97531</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>146582</t>
+          <t>145801</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>112929</t>
+          <t>116411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>163396</t>
+          <t>165810</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>225645</t>
+          <t>229446</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>291627</t>
+          <t>293670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>164035</t>
+          <t>167800</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>239357</t>
+          <t>240626</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>154883</t>
+          <t>154867</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>221987</t>
+          <t>220612</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>340213</t>
+          <t>335765</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>440108</t>
+          <t>442886</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1599957</t>
+          <t>1596611</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1683765</t>
+          <t>1680009</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1395729</t>
+          <t>1393891</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1474263</t>
+          <t>1469820</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3008333</t>
+          <t>3012711</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3125014</t>
+          <t>3128178</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,05%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22719</t>
+          <t>21896</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48518</t>
+          <t>48740</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31804</t>
+          <t>30216</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59075</t>
+          <t>57600</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>58795</t>
+          <t>59615</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>96188</t>
+          <t>97344</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65909</t>
+          <t>66424</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111538</t>
+          <t>111519</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70268</t>
+          <t>70163</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113458</t>
+          <t>113817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>147410</t>
+          <t>148106</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208936</t>
+          <t>208480</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>336531</t>
+          <t>337519</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>383146</t>
+          <t>383180</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>302597</t>
+          <t>300778</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>346988</t>
+          <t>344162</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>652298</t>
+          <t>654183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>717473</t>
+          <t>717759</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,37%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>178827</t>
+          <t>179557</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>242234</t>
+          <t>238901</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>200258</t>
+          <t>203217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>263092</t>
+          <t>268155</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>396131</t>
+          <t>398064</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>486232</t>
+          <t>486162</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>308699</t>
+          <t>315363</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>406882</t>
+          <t>410647</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>305924</t>
+          <t>310668</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399726</t>
+          <t>403362</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>648670</t>
+          <t>649693</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>780710</t>
+          <t>787749</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2799603</t>
+          <t>2800307</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2908657</t>
+          <t>2907745</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2916540</t>
+          <t>2918473</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3023030</t>
+          <t>3022563</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5741585</t>
+          <t>5738801</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5894612</t>
+          <t>5896132</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2016</t>
+          <t>Población según su lugar de nacimiento en 2016 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>15259</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37870</t>
+          <t>38379</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25140</t>
+          <t>25878</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50944</t>
+          <t>50181</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47471</t>
+          <t>48138</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80855</t>
+          <t>79147</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28316</t>
+          <t>27358</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60789</t>
+          <t>57707</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,47 +4971,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>53716</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>37261</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>74975</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>3,75%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8,06%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>53716</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>35699</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>74399</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73821</t>
+          <t>74083</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121507</t>
+          <t>125267</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>667555</t>
+          <t>668549</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>703814</t>
+          <t>705640</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,47 +5084,47 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>88,63%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>93,54%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>904414</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>880207</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>922416</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>90,93%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>88,49%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>93,3%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>829</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>904414</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>879661</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>925892</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>90,93%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>88,44%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1563596</t>
+          <t>1562199</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1617999</t>
+          <t>1616091</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118238</t>
+          <t>118774</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>168606</t>
+          <t>167963</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>111853</t>
+          <t>111764</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>156370</t>
+          <t>157219</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>242115</t>
+          <t>242429</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>312787</t>
+          <t>311796</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>152836</t>
+          <t>150228</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>217609</t>
+          <t>218086</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>171222</t>
+          <t>172283</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>235907</t>
+          <t>237637</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>342826</t>
+          <t>339138</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>432626</t>
+          <t>433329</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1711600</t>
+          <t>1709677</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1789676</t>
+          <t>1793448</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,82 +5540,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>82,34%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>86,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1663</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1652487</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1612414</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1690145</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>83,11%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>81,1%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>85,0%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>3403347</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>3350586</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3459560</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>83,73%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>82,43%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>86,19%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1663</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1652487</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1616278</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1689205</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>83,11%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>81,29%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>84,96%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>3400</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>3403347</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>3353789</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3461033</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>83,73%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>82,51%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,11%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26803</t>
+          <t>26236</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53077</t>
+          <t>53696</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45781</t>
+          <t>44606</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76247</t>
+          <t>75824</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>80578</t>
+          <t>79732</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>118613</t>
+          <t>120178</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69019</t>
+          <t>70437</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111921</t>
+          <t>113808</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50702</t>
+          <t>53374</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89176</t>
+          <t>90496</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132056</t>
+          <t>132377</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189784</t>
+          <t>192879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>393772</t>
+          <t>392769</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>439270</t>
+          <t>438710</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>395882</t>
+          <t>398615</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>442453</t>
+          <t>440663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>803722</t>
+          <t>800069</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>867666</t>
+          <t>870521</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,43%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>176933</t>
+          <t>179671</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>241570</t>
+          <t>242340</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>199846</t>
+          <t>198798</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>258506</t>
+          <t>258593</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>394005</t>
+          <t>396910</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>479609</t>
+          <t>481392</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>272262</t>
+          <t>273110</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>359310</t>
+          <t>359479</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>281178</t>
+          <t>280796</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>371485</t>
+          <t>371985</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>583866</t>
+          <t>579991</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>706653</t>
+          <t>697542</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2804751</t>
+          <t>2800919</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2905800</t>
+          <t>2901923</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2927122</t>
+          <t>2927921</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3032300</t>
+          <t>3026273</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5756220</t>
+          <t>5762160</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5898035</t>
+          <t>5902487</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2023</t>
+          <t>Población según su lugar de nacimiento en 2023 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,82 +6913,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6784</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4816</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8890</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>13066</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>10623</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>16353</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6784</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4990</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8917</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>13066</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>10348</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>16541</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>17953</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14355</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27255</t>
+          <t>26976</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22176</t>
+          <t>22191</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41190</t>
+          <t>39663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>490983</t>
+          <t>490817</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>503986</t>
+          <t>503759</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>711867</t>
+          <t>712255</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725314</t>
+          <t>725679</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1207008</t>
+          <t>1207739</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1226674</t>
+          <t>1226151</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21056</t>
+          <t>21197</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29237</t>
+          <t>29221</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33533</t>
+          <t>33260</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43491</t>
+          <t>43600</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>57182</t>
+          <t>57050</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70094</t>
+          <t>70086</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80672</t>
+          <t>79911</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>127341</t>
+          <t>129285</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>79705</t>
+          <t>79596</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>111709</t>
+          <t>112670</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>168620</t>
+          <t>170064</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>224798</t>
+          <t>228137</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1891888</t>
+          <t>1891388</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1940893</t>
+          <t>1941107</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1777890</t>
+          <t>1776586</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1813061</t>
+          <t>1810131</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3685680</t>
+          <t>3679560</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3743546</t>
+          <t>3739892</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11273</t>
+          <t>11573</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11365</t>
+          <t>11594</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17867</t>
+          <t>17937</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19099</t>
+          <t>19621</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27049</t>
+          <t>27207</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52261</t>
+          <t>51875</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84438</t>
+          <t>85732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44513</t>
+          <t>45549</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68565</t>
+          <t>69279</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102629</t>
+          <t>105146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>144335</t>
+          <t>144429</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>544530</t>
+          <t>543860</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>576972</t>
+          <t>577809</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>574268</t>
+          <t>573724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>598945</t>
+          <t>599324</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1128711</t>
+          <t>1128754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1170119</t>
+          <t>1168557</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34916</t>
+          <t>34715</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45428</t>
+          <t>45619</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53856</t>
+          <t>53743</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66194</t>
+          <t>66489</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91575</t>
+          <t>91911</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107751</t>
+          <t>107943</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151976</t>
+          <t>152662</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209282</t>
+          <t>210308</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>149230</t>
+          <t>149523</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192848</t>
+          <t>192542</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>312690</t>
+          <t>317131</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>387417</t>
+          <t>384773</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2950411</t>
+          <t>2948783</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3007551</t>
+          <t>3007320</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3078351</t>
+          <t>3079227</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3124078</t>
+          <t>3124042</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6042390</t>
+          <t>6044785</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6118797</t>
+          <t>6115572</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P58-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P58-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47220</t>
+          <t>45698</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85780</t>
+          <t>84585</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22708</t>
+          <t>22088</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51126</t>
+          <t>51992</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77301</t>
+          <t>76997</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125407</t>
+          <t>124543</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25584</t>
+          <t>25563</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56344</t>
+          <t>55742</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51278</t>
+          <t>51262</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85033</t>
+          <t>85997</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84012</t>
+          <t>83984</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131546</t>
+          <t>129866</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>903144</t>
+          <t>902453</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>950127</t>
+          <t>949646</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1192680</t>
+          <t>1188631</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1233175</t>
+          <t>1234194</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2104294</t>
+          <t>2109986</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2170359</t>
+          <t>2170824</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76247</t>
+          <t>75985</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>126652</t>
+          <t>123572</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116948</t>
+          <t>115718</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>173456</t>
+          <t>168949</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>207425</t>
+          <t>209117</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>279450</t>
+          <t>284119</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>126841</t>
+          <t>124419</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>186964</t>
+          <t>182490</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,82 +1317,82 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>10,78%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>128046</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>105345</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>151395</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>9,54%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>281224</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>245774</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>320833</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>7,49%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>11,04%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>128046</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108086</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>153000</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>9,64%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>281224</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>244432</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>321081</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1400478</t>
+          <t>1404093</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1471738</t>
+          <t>1477121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1283751</t>
+          <t>1281558</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1350305</t>
+          <t>1354359</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2707388</t>
+          <t>2706419</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2802511</t>
+          <t>2804504</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27275</t>
+          <t>27709</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58557</t>
+          <t>57902</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33633</t>
+          <t>33293</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66270</t>
+          <t>64310</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69900</t>
+          <t>69255</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115085</t>
+          <t>112662</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61369</t>
+          <t>59500</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102879</t>
+          <t>100302</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40937</t>
+          <t>41399</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72355</t>
+          <t>69707</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111570</t>
+          <t>113110</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>164692</t>
+          <t>163112</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>404726</t>
+          <t>407436</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>452769</t>
+          <t>454892</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>352360</t>
+          <t>354713</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>391780</t>
+          <t>392704</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>767771</t>
+          <t>772677</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>831774</t>
+          <t>834985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,24%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>174306</t>
+          <t>172478</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>239426</t>
+          <t>242923</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>192710</t>
+          <t>192321</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>260917</t>
+          <t>264557</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>381417</t>
+          <t>381036</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>484671</t>
+          <t>478948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>235995</t>
+          <t>235468</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>316319</t>
+          <t>318025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>220515</t>
+          <t>217477</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>282692</t>
+          <t>280146</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>476262</t>
+          <t>471995</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>580058</t>
+          <t>578127</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2749724</t>
+          <t>2745881</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2847351</t>
+          <t>2848050</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2858073</t>
+          <t>2857046</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2946200</t>
+          <t>2948671</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5630879</t>
+          <t>5640007</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5772031</t>
+          <t>5775166</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37916</t>
+          <t>37759</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69269</t>
+          <t>69230</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37218</t>
+          <t>35121</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66848</t>
+          <t>65248</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80187</t>
+          <t>83516</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125108</t>
+          <t>127555</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51132</t>
+          <t>51506</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95594</t>
+          <t>97031</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54841</t>
+          <t>56213</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99456</t>
+          <t>100458</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117349</t>
+          <t>119130</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>182489</t>
+          <t>180942</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>823552</t>
+          <t>820875</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>876362</t>
+          <t>872201</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1186077</t>
+          <t>1183903</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1237000</t>
+          <t>1233509</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2023992</t>
+          <t>2025721</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2099391</t>
+          <t>2096985</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97531</t>
+          <t>102210</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>145801</t>
+          <t>149442</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116411</t>
+          <t>115076</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>165810</t>
+          <t>163115</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>229446</t>
+          <t>229937</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>293670</t>
+          <t>295333</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>167800</t>
+          <t>166154</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>240626</t>
+          <t>241405</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>154867</t>
+          <t>154154</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>220612</t>
+          <t>222533</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>335765</t>
+          <t>336639</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>442886</t>
+          <t>439880</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1596611</t>
+          <t>1592982</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1680009</t>
+          <t>1679329</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1393891</t>
+          <t>1393541</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1469820</t>
+          <t>1472694</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3012711</t>
+          <t>3017605</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3128178</t>
+          <t>3128806</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,07%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21896</t>
+          <t>22556</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48740</t>
+          <t>46818</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30216</t>
+          <t>30162</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57600</t>
+          <t>56687</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>59615</t>
+          <t>58441</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>97344</t>
+          <t>94496</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66424</t>
+          <t>65392</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111519</t>
+          <t>110354</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70163</t>
+          <t>70797</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113817</t>
+          <t>114357</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>148106</t>
+          <t>148645</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208480</t>
+          <t>210996</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,45%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>337519</t>
+          <t>337504</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>383180</t>
+          <t>385769</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>300778</t>
+          <t>300271</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>344162</t>
+          <t>347242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>654183</t>
+          <t>649845</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>717759</t>
+          <t>717014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>179557</t>
+          <t>177585</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>238901</t>
+          <t>238580</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>203217</t>
+          <t>203192</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>268155</t>
+          <t>264784</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>398064</t>
+          <t>394647</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>486162</t>
+          <t>484269</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>315363</t>
+          <t>307063</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>410647</t>
+          <t>411020</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>310668</t>
+          <t>309829</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>403362</t>
+          <t>401176</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>649693</t>
+          <t>645378</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>787749</t>
+          <t>785887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2800307</t>
+          <t>2795802</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2907745</t>
+          <t>2912973</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2918473</t>
+          <t>2915310</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3022563</t>
+          <t>3020728</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5738801</t>
+          <t>5746062</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5896132</t>
+          <t>5896935</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,56%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15259</t>
+          <t>15586</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38379</t>
+          <t>37196</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25878</t>
+          <t>24790</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50181</t>
+          <t>48379</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48138</t>
+          <t>47346</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79147</t>
+          <t>78857</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27358</t>
+          <t>28362</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57707</t>
+          <t>59866</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37261</t>
+          <t>38971</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74975</t>
+          <t>77536</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74083</t>
+          <t>74386</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125267</t>
+          <t>122767</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>668549</t>
+          <t>667429</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>705640</t>
+          <t>704688</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>880207</t>
+          <t>878754</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>922416</t>
+          <t>923873</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1562199</t>
+          <t>1562477</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1616091</t>
+          <t>1617469</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118774</t>
+          <t>119266</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>167963</t>
+          <t>173215</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>111764</t>
+          <t>111150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>157219</t>
+          <t>155484</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>242429</t>
+          <t>243148</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>311796</t>
+          <t>317994</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>150228</t>
+          <t>153093</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>218086</t>
+          <t>215352</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>172283</t>
+          <t>173042</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>237637</t>
+          <t>240427</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>339138</t>
+          <t>341859</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433329</t>
+          <t>436349</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1709677</t>
+          <t>1708692</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1793448</t>
+          <t>1786850</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1612414</t>
+          <t>1611003</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1690145</t>
+          <t>1688074</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3350586</t>
+          <t>3342508</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3459560</t>
+          <t>3458233</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,08%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26236</t>
+          <t>26750</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53696</t>
+          <t>55263</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44606</t>
+          <t>44839</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75824</t>
+          <t>75368</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>79732</t>
+          <t>80175</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120178</t>
+          <t>121026</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70437</t>
+          <t>70890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113808</t>
+          <t>114679</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53374</t>
+          <t>50577</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90496</t>
+          <t>88591</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132377</t>
+          <t>133030</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192879</t>
+          <t>190683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>392769</t>
+          <t>391899</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>438710</t>
+          <t>439655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>398615</t>
+          <t>398519</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>440663</t>
+          <t>443225</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>800069</t>
+          <t>803441</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>870521</t>
+          <t>868972</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,28%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>179671</t>
+          <t>177697</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>242340</t>
+          <t>238620</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>198798</t>
+          <t>201791</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>258593</t>
+          <t>262405</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>396910</t>
+          <t>394353</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>481392</t>
+          <t>481982</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>273110</t>
+          <t>274061</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>359479</t>
+          <t>356647</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>280796</t>
+          <t>285452</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>371985</t>
+          <t>367628</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>579991</t>
+          <t>583051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>697542</t>
+          <t>703253</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2800919</t>
+          <t>2805196</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2901923</t>
+          <t>2904740</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2927921</t>
+          <t>2929604</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3026273</t>
+          <t>3024333</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5762160</t>
+          <t>5764607</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5902487</t>
+          <t>5903114</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,43%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>48314</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>34539</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8678</t>
+          <t>69166</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>30547</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>22284</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>40185</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>78861</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>62465</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16353</t>
+          <t>100031</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9992</t>
+          <t>10551</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17953</t>
+          <t>19624</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20011</t>
+          <t>21223</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14355</t>
+          <t>15232</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26976</t>
+          <t>28967</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>30003</t>
+          <t>31774</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22191</t>
+          <t>23802</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39663</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>498664</t>
+          <t>519664</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>490817</t>
+          <t>497653</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>503759</t>
+          <t>534771</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>719255</t>
+          <t>768357</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>712255</t>
+          <t>755734</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725679</t>
+          <t>778200</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1217921</t>
+          <t>1288021</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1207739</t>
+          <t>1264737</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1226151</t>
+          <t>1306447</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>93,41%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>746051</t>
+          <t>820127</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>746051</t>
+          <t>820127</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>746051</t>
+          <t>820127</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1260990</t>
+          <t>1398656</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1260990</t>
+          <t>1398656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1260990</t>
+          <t>1398656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>24913</t>
+          <t>186256</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21197</t>
+          <t>157407</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29221</t>
+          <t>218748</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>195813</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33260</t>
+          <t>171219</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43600</t>
+          <t>226589</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>63253</t>
+          <t>382068</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>57050</t>
+          <t>342121</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70086</t>
+          <t>423330</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>100989</t>
+          <t>98715</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79911</t>
+          <t>78052</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>129285</t>
+          <t>123310</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94156</t>
+          <t>96835</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>79596</t>
+          <t>81498</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>112670</t>
+          <t>115537</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>195145</t>
+          <t>195551</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>170064</t>
+          <t>168127</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>228137</t>
+          <t>225941</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1919745</t>
+          <t>1944455</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1891388</t>
+          <t>1907645</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1941107</t>
+          <t>1981735</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1795733</t>
+          <t>1874687</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1776586</t>
+          <t>1838166</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1810131</t>
+          <t>1902574</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3715478</t>
+          <t>3819142</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3679560</t>
+          <t>3767569</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3739892</t>
+          <t>3869637</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>88,01%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2045647</t>
+          <t>2229426</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2045647</t>
+          <t>2229426</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2045647</t>
+          <t>2229426</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1928229</t>
+          <t>2167335</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1928229</t>
+          <t>2167335</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1928229</t>
+          <t>2167335</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3973876</t>
+          <t>4396761</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3973876</t>
+          <t>4396761</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3973876</t>
+          <t>4396761</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>59230</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>44331</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11573</t>
+          <t>77390</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14594</t>
+          <t>67998</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11594</t>
+          <t>54180</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17937</t>
+          <t>84098</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>23250</t>
+          <t>127229</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>106319</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27207</t>
+          <t>151940</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>66523</t>
+          <t>69232</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51875</t>
+          <t>53599</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85732</t>
+          <t>86751</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56048</t>
+          <t>57705</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45549</t>
+          <t>46066</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69279</t>
+          <t>71689</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>122571</t>
+          <t>126937</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105146</t>
+          <t>108510</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>144429</t>
+          <t>150046</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -8031,69 +8031,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>562483</t>
+          <t>581943</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>543860</t>
+          <t>559042</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>577809</t>
+          <t>603402</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>78,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>84,94%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>606787</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>587455</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>624713</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>82,84%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>80,2%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>85,29%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,61%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>826</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>587529</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>573724</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>599324</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>89,27%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>87,17%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>91,06%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1385</t>
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1150013</t>
+          <t>1188730</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1128754</t>
+          <t>1158020</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1168557</t>
+          <t>1214174</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>84,15%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>637662</t>
+          <t>710405</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>637662</t>
+          <t>710405</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>637662</t>
+          <t>710405</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>658171</t>
+          <t>732490</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>658171</t>
+          <t>732490</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>658171</t>
+          <t>732490</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1295834</t>
+          <t>1442895</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1295834</t>
+          <t>1442895</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1295834</t>
+          <t>1442895</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>39851</t>
+          <t>293800</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34715</t>
+          <t>257084</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45619</t>
+          <t>334857</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>59718</t>
+          <t>294358</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53743</t>
+          <t>263413</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66489</t>
+          <t>327481</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>99569</t>
+          <t>588158</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91911</t>
+          <t>541258</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107943</t>
+          <t>642393</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>177504</t>
+          <t>178498</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152662</t>
+          <t>148909</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210308</t>
+          <t>208409</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>170215</t>
+          <t>175763</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>149523</t>
+          <t>155323</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192542</t>
+          <t>199082</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>347719</t>
+          <t>354261</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>317131</t>
+          <t>318382</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>384773</t>
+          <t>394880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2980893</t>
+          <t>3046062</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2948783</t>
+          <t>2995744</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3007320</t>
+          <t>3090041</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3102519</t>
+          <t>3249831</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3079227</t>
+          <t>3212396</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3124042</t>
+          <t>3288235</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6083411</t>
+          <t>6295893</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6044785</t>
+          <t>6233393</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6115572</t>
+          <t>6357381</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>87,83%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3198248</t>
+          <t>3518360</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3198248</t>
+          <t>3518360</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3198248</t>
+          <t>3518360</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3332452</t>
+          <t>3719952</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3332452</t>
+          <t>3719952</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3332452</t>
+          <t>3719952</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>6530699</t>
+          <t>7238312</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6530699</t>
+          <t>7238312</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6530699</t>
+          <t>7238312</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
